--- a/forms/trg/Formulir_TRG_mc-nutrition.xlsx
+++ b/forms/trg/Formulir_TRG_mc-nutrition.xlsx
@@ -940,7 +940,11 @@
           <t>Prof. dr. Veni Hadju, MSc, PhD</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -1176,7 +1180,11 @@
           <t>Suriyanti, S.Keb</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n"/>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
@@ -1201,7 +1209,11 @@
           <t>dr. Ardiansyah, S.Ked., M.Kes</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="12" t="n"/>
@@ -1226,7 +1238,11 @@
           <t>Ainurafiq, S.KM., M.Kes</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n"/>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="12" t="n"/>
@@ -1251,7 +1267,11 @@
           <t>Andi Ardi</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D16" s="12" t="n"/>
       <c r="E16" s="11" t="n"/>
       <c r="F16" s="12" t="n"/>
@@ -1276,7 +1296,11 @@
           <t>Suryanti</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n"/>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D17" s="12" t="n"/>
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="12" t="n"/>
@@ -1301,7 +1325,11 @@
           <t>Musfirah</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n"/>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D18" s="12" t="n"/>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="12" t="n"/>
@@ -1326,7 +1354,11 @@
           <t>Ernawati, SST, Bd, M.Kes</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n"/>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D19" s="12" t="n"/>
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="12" t="n"/>
@@ -1351,7 +1383,11 @@
           <t>Nelly Nugrawati, SST, Bd, M.Kes</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D20" s="12" t="n"/>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="12" t="n"/>
@@ -1376,7 +1412,11 @@
           <t>Sahwin Permadi Yahya, S.Tr.Gz,M.Gz</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n"/>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D21" s="12" t="n"/>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="12" t="n"/>
@@ -1401,7 +1441,11 @@
           <t>La Ode Ahmad Mardin S.Gz, M.Gz</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n"/>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D22" s="12" t="n"/>
       <c r="E22" s="11" t="n"/>
       <c r="F22" s="12" t="n"/>
@@ -1426,7 +1470,11 @@
           <t>Amirul Mukminin, S.Gz</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n"/>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D23" s="12" t="n"/>
       <c r="E23" s="11" t="n"/>
       <c r="F23" s="12" t="n"/>
@@ -1451,7 +1499,11 @@
           <t>Dian Lestari, S.Gz., M.Gz</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n"/>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D24" s="12" t="n"/>
       <c r="E24" s="11" t="n"/>
       <c r="F24" s="12" t="n"/>
@@ -1476,7 +1528,11 @@
           <t>Asniar, SKM., M.Gz</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n"/>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D25" s="12" t="n"/>
       <c r="E25" s="11" t="n"/>
       <c r="F25" s="12" t="n"/>
@@ -1501,7 +1557,11 @@
           <t>Febriyanti, S.K.M.,M.Gz</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n"/>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D26" s="12" t="n"/>
       <c r="E26" s="11" t="n"/>
       <c r="F26" s="12" t="n"/>
@@ -1526,7 +1586,11 @@
           <t>Salwa Afifah Yusrina, S.Gz., M.Gz</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n"/>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D27" s="12" t="n"/>
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="12" t="n"/>
@@ -1551,7 +1615,11 @@
           <t>Afifah Zahra</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n"/>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D28" s="12" t="n"/>
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="12" t="n"/>
@@ -1576,7 +1644,11 @@
           <t>Nurul Fadhilah</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n"/>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D29" s="12" t="n"/>
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="12" t="n"/>
@@ -1601,7 +1673,11 @@
           <t>Kansyah Mahira</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n"/>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D30" s="12" t="n"/>
       <c r="E30" s="11" t="n"/>
       <c r="F30" s="12" t="n"/>
@@ -1626,7 +1702,11 @@
           <t>Angryni Benyamin</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n"/>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D31" s="12" t="n"/>
       <c r="E31" s="11" t="n"/>
       <c r="F31" s="12" t="n"/>
@@ -1651,7 +1731,11 @@
           <t>Nabila Nur Rakhma, S.Gz</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n"/>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D32" s="12" t="n"/>
       <c r="E32" s="11" t="n"/>
       <c r="F32" s="12" t="n"/>
@@ -1676,7 +1760,11 @@
           <t>Nurul Annisa Arifuddin, S.Gz</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D33" s="12" t="n"/>
       <c r="E33" s="11" t="n"/>
       <c r="F33" s="12" t="n"/>
